--- a/artfynd/A 21150-2022 artfynd.xlsx
+++ b/artfynd/A 21150-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21150-2022 artfynd.xlsx
+++ b/artfynd/A 21150-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13754810</v>
+        <v>13754809</v>
       </c>
       <c r="B2" t="n">
-        <v>42704</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>694379.7848563661</v>
+        <v>694430</v>
       </c>
       <c r="R2" t="n">
-        <v>6656813.738444501</v>
+        <v>6656794</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,19 +757,9 @@
           <t>2008-08-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-09-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -811,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>14619868</v>
+        <v>13754810</v>
       </c>
       <c r="B3" t="n">
-        <v>42704</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,7 +826,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -865,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>694376.3596698872</v>
+        <v>694380</v>
       </c>
       <c r="R3" t="n">
-        <v>6656821.575427857</v>
+        <v>6656814</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,22 +875,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2010-08-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-08-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2010-09-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -947,15 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>14619869</v>
+        <v>14619866</v>
       </c>
       <c r="B4" t="n">
-        <v>42704</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +947,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1001,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>694383.446557317</v>
+        <v>694434</v>
       </c>
       <c r="R4" t="n">
-        <v>6656820.446023572</v>
+        <v>6656794</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1034,19 +999,9 @@
           <t>2010-08-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2010-09-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1083,15 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73882426</v>
+        <v>14619867</v>
       </c>
       <c r="B5" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,12 +1068,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>kolonier</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,11 +1076,6 @@
           <t>larv/nymf</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1143,14 +1083,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Borgskogen, Upl</t>
+          <t>Norrtälje kommun, Ununge och Edebo församlingar, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>694304.1737114949</v>
+        <v>694429</v>
       </c>
       <c r="R5" t="n">
-        <v>6656838.813932405</v>
+        <v>6656795</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1177,22 +1117,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Inventeringen utfördes för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Stockholms län.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,49 +1139,30 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>olvon</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Viburnum opulus</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Viburnum opulus</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Hyggen med uppväxande ask och olvon</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Arvid Löf</t>
+          <t>Elisabeth Hedin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Arvid Löf, Jan-Olov Björklund</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Elisabeth Hedin, Jan-Olov Björklund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96850048</v>
+        <v>14619868</v>
       </c>
       <c r="B6" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,12 +1189,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>kolonier</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1286,16 +1197,21 @@
           <t>larv/nymf</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Borgskogen, Upl</t>
+          <t>Norrtälje kommun, Ununge och Edebo församlingar, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>694381.365233734</v>
+        <v>694376</v>
       </c>
       <c r="R6" t="n">
-        <v>6656821.839526232</v>
+        <v>6656822</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1322,22 +1238,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Inventeringen utfördes för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Stockholms län.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1349,49 +1260,30 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Hyggen med uppväxande ask och olvon</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
+          <t>Elisabeth Hedin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Lif</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Elisabeth Hedin, Jan-Olov Björklund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105041057</v>
+        <v>14619869</v>
       </c>
       <c r="B7" t="n">
-        <v>42705</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1421,29 +1313,26 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>larv/nymf</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Borgskogen, Upl</t>
+          <t>Norrtälje kommun, Ununge och Edebo församlingar, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>694372.3024895665</v>
+        <v>694383</v>
       </c>
       <c r="R7" t="n">
-        <v>6656822.36358311</v>
+        <v>6656820</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1470,22 +1359,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-08-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-09-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Inventeringen utfördes för Norrtälje Naturvårdsstiftelse på uppdrag av Länsstyrelsen i Stockholms län.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1494,37 +1378,561 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Hyggen med uppväxande ask och olvon</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Elisabeth Hedin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elisabeth Hedin, Jan-Olov Björklund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>73882426</v>
+      </c>
+      <c r="B8" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Borgskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>694304</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6656839</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>olvon</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Viburnum opulus</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Viburnum opulus</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Arvid Löf</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Arvid Löf, Jan-Olov Björklund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>80758732</v>
+      </c>
+      <c r="B9" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Borgskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>694427</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6656796</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2019-09-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2019-09-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Arvid Löf</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Arvid Löf, Jan-Olov Björklund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>96850048</v>
+      </c>
+      <c r="B10" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Borgskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>694382</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6656822</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-09-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>105041057</v>
+      </c>
+      <c r="B11" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Borgskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>694373</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6656823</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-09-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-09-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Mårten Nilsson</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Mårten Nilsson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>

--- a/artfynd/A 21150-2022 artfynd.xlsx
+++ b/artfynd/A 21150-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754809</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13754810</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14619866</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14619867</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,6 +1302,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14619868</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1398,6 +1428,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14619869</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1538,6 +1573,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73882426</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1673,6 +1713,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80758732</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1803,6 +1848,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850048</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1937,8 +1987,25 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105041057</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>